--- a/tests/test_outputs/meta_export_20260228.xlsx
+++ b/tests/test_outputs/meta_export_20260228.xlsx
@@ -351,10 +351,601 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:CN2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1"/>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>article_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>article_num</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>author</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>doi_clean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>reviewed_by</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reviewed_at</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>location_osm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>bounding_box_label</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>habitat_type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>country_name</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>is_experimental</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>group_instance</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>site_name</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>test_multi</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>test_date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>yi</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>effect_status</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>raw_n</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>raw_df</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sd_X</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sd_Y</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>raw_se_r</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>raw_t_stat</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>raw_r_reported</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>raw_study_design</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>raw_study_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>raw_covariance_XY</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>raw_response_unit</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>raw_predictor_unit</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_response_scale</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>raw_interaction_effect</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>raw_response_distribution</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>raw_predictor_distribution</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>raw_response_variable_name</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>raw_predictor_variable_name</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>raw_F_stat</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_p_value</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>raw_n_control</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>raw_n_treatment</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>raw_mean_control</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>raw_mean_treatment</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>raw_chi_square_stat</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>raw_var_value_control</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>raw_var_statistic_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>raw_control_description</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_use_small_sd_approx</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>raw_var_value_treatment</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>raw_treatment_description</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>raw_beta</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>raw_se_beta</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>raw_multiple_predictors</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>raw_beta_type</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>raw_n_predictors</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_df</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_F_stat</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_t_stat</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_p_value</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_n_control</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_n_treatment</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_mean_control</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_study_design</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_mean_treatment</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_chi_square_stat</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_var_value_control</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_var_statistic_type</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_control_description</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_use_small_sd_approx</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_var_value_treatment</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_a_treatment_description</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_df</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_F_stat</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_t_stat</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_p_value</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_n_control</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_n_treatment</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_mean_control</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_study_design</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_mean_treatment</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_chi_square_stat</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_var_value_control</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_var_statistic_type</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_control_description</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_use_small_sd_approx</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_var_value_treatment</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>raw_group_b_treatment_description</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>raw_interaction_pathway</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fe938548-ee91-4d96-a3b1-48f452e33e9e</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Freshwater fish diversity responses to dam removal across temperate watersheds</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Huang JX; Torres MM; Eriksen S</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2020</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10.1007/s10750-020-04321-y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>564c9186-f70d-47f2-b285-55baee74f705</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-02-28T15:25:37+00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>lon_min=-40; lon_max=40; lat_min=0; lat_max=20</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Grassland</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>study_site</t>
+        </is>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Test effect size 2</t>
+        </is>
+      </c>
+      <c r="T2">
+        <v>0.8</v>
+      </c>
+      <c r="U2">
+        <v>1.09861228866811</v>
+      </c>
+      <c r="V2">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>correlation</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Experimental (ex-situ)</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Ind. behaviour</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tests/test_outputs/meta_export_20260228.xlsx
+++ b/tests/test_outputs/meta_export_20260228.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CN2"/>
+  <dimension ref="A1:CC6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -562,285 +562,230 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>raw_F_stat</t>
+          <t>raw_beta</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>raw_se_beta</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>raw_p_value</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>raw_n_control</t>
-        </is>
-      </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>raw_n_treatment</t>
+          <t>raw_multiple_predictors</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>raw_mean_control</t>
+          <t>raw_beta_type</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>raw_mean_treatment</t>
+          <t>raw_n_predictors</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>raw_chi_square_stat</t>
+          <t>raw_group_a_df</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>raw_var_value_control</t>
+          <t>raw_group_a_F_stat</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>raw_var_statistic_type</t>
+          <t>raw_group_a_t_stat</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>raw_control_description</t>
+          <t>raw_group_a_p_value</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>raw_use_small_sd_approx</t>
+          <t>raw_group_a_n_control</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>raw_var_value_treatment</t>
+          <t>raw_group_a_n_treatment</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>raw_treatment_description</t>
+          <t>raw_group_a_mean_control</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>raw_beta</t>
+          <t>raw_group_a_study_design</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>raw_se_beta</t>
+          <t>raw_group_a_mean_treatment</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>raw_multiple_predictors</t>
+          <t>raw_group_a_chi_square_stat</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>raw_beta_type</t>
+          <t>raw_group_a_var_value_control</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>raw_n_predictors</t>
+          <t>raw_group_a_var_statistic_type</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_df</t>
+          <t>raw_group_a_control_description</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_F_stat</t>
+          <t>raw_group_a_use_small_sd_approx</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_t_stat</t>
+          <t>raw_group_a_var_value_treatment</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_p_value</t>
+          <t>raw_group_a_treatment_description</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_n_control</t>
+          <t>raw_group_b_df</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_n_treatment</t>
+          <t>raw_group_b_F_stat</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_mean_control</t>
+          <t>raw_group_b_t_stat</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_study_design</t>
+          <t>raw_group_b_p_value</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_mean_treatment</t>
+          <t>raw_group_b_n_control</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_chi_square_stat</t>
+          <t>raw_group_b_n_treatment</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_var_value_control</t>
+          <t>raw_group_b_mean_control</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_var_statistic_type</t>
+          <t>raw_group_b_study_design</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_control_description</t>
+          <t>raw_group_b_mean_treatment</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_use_small_sd_approx</t>
+          <t>raw_group_b_chi_square_stat</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_var_value_treatment</t>
+          <t>raw_group_b_var_value_control</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_a_treatment_description</t>
+          <t>raw_group_b_var_statistic_type</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_b_df</t>
+          <t>raw_group_b_control_description</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_b_F_stat</t>
+          <t>raw_group_b_use_small_sd_approx</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_b_t_stat</t>
+          <t>raw_group_b_var_value_treatment</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_b_p_value</t>
+          <t>raw_group_b_treatment_description</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_b_n_control</t>
+          <t>raw_interaction_pathway</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>raw_group_b_n_treatment</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_mean_control</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_study_design</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_mean_treatment</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_chi_square_stat</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_var_value_control</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_var_statistic_type</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_control_description</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_use_small_sd_approx</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_var_value_treatment</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>raw_group_b_treatment_description</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>raw_interaction_pathway</t>
+          <t>meta_flag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fe938548-ee91-4d96-a3b1-48f452e33e9e</t>
+          <t>6b26fc7f-966b-4fe8-8065-d5d00cdecdd8</t>
         </is>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Freshwater fish diversity responses to dam removal across temperate watersheds</t>
+          <t>Sexual selection and mate choice in socially monogamous passerine birds</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Huang JX; Torres MM; Eriksen S</t>
+          <t>Valente EF; Costa PA; Dumont R</t>
         </is>
       </c>
       <c r="E2">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.1007/s10750-020-04321-y</t>
+          <t>10.1098/rspb.2017.2389</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -855,17 +800,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-02-28T15:25:37+00:00</t>
+          <t>2026-03-01T11:52:42+00:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Paris, Ile-de-France, Metropolitan France, France; 48.8589; 2.32; 7444</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>lon_min=-40; lon_max=40; lat_min=0; lat_max=20</t>
+          <t>lon_min=; lon_max=; lat_min=; lat_max=</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Grassland</t>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>frn</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -879,11 +834,11 @@
         </is>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Test effect size 2</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="T2">
@@ -922,27 +877,701 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>Observational</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Ind. health or growth</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6b26fc7f-966b-4fe8-8065-d5d00cdecdd8</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sexual selection and mate choice in socially monogamous passerine birds</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Valente EF; Costa PA; Dumont R</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>2017</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.1098/rspb.2017.2389</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>564c9186-f70d-47f2-b285-55baee74f705</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-03-01T11:52:42+00:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Paris, Ile-de-France, Metropolitan France, France; 48.8589; 2.32; 7444</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>lon_min=; lon_max=; lat_min=; lat_max=</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frn</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>study_site</t>
+        </is>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Interaction pathway B</t>
+        </is>
+      </c>
+      <c r="T3">
+        <v>-0.2737345791026131</v>
+      </c>
+      <c r="U3">
+        <v>-0.2808964681192619</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>calculated_relative</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Observational</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Ind. health or growth</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>control_treatment</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>control_treatment</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>vi_missing (enter sample size n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4f8fa6f3-7345-494c-a01e-fdd0d6a6e0f0</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Soil microbial community responses to nitrogen enrichment in alpine meadows</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Okonkwo CE; Svensson AB; Pires LM</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>2016</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.1890/15-1432.1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>564c9186-f70d-47f2-b285-55baee74f705</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-03-01T11:21:49+00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Toronto, Golden Horseshoe, Ontario, Canada; 43.6535; -79.3839; 324211</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>lon_min=; lon_max=; lat_min=; lat_max=</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Grassland</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>invited reviewer test</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>study_site</t>
+        </is>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Interaction path B</t>
+        </is>
+      </c>
+      <c r="T4">
+        <v>-0.4700130862035674</v>
+      </c>
+      <c r="U4">
+        <v>-0.5100871333106207</v>
+      </c>
+      <c r="V4">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>calculated_relative</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>Experimental (ex-situ)</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Pop. size</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Proportion</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>control_treatment</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>control_treatment</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fe938548-ee91-4d96-a3b1-48f452e33e9e</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Freshwater fish diversity responses to dam removal across temperate watersheds</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Huang JX; Torres MM; Eriksen S</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>2020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.1007/s10750-020-04321-y</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>564c9186-f70d-47f2-b285-55baee74f705</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-03-01T11:27:57+00:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>lon_min=-40; lon_max=40; lat_min=0; lat_max=20</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Grassland</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>study_site</t>
+        </is>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Correlation test</t>
+        </is>
+      </c>
+      <c r="T5">
+        <v>0.8</v>
+      </c>
+      <c r="U5">
+        <v>1.09861228866811</v>
+      </c>
+      <c r="V5">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>correlation</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fe938548-ee91-4d96-a3b1-48f452e33e9e</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Freshwater fish diversity responses to dam removal across temperate watersheds</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Huang JX; Torres MM; Eriksen S</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>2020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10.1007/s10750-020-04321-y</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>564c9186-f70d-47f2-b285-55baee74f705</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-03-01T11:27:57+00:00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>lon_min=-40; lon_max=40; lat_min=0; lat_max=20</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Grassland</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>study_site</t>
+        </is>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Interaction pathway A</t>
+        </is>
+      </c>
+      <c r="T6">
+        <v>0.1621424235993525</v>
+      </c>
+      <c r="U6">
+        <v>0.1635861840335697</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Simulation</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Ind. behaviour</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Categorical</t>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>vi_missing (enter sample size n)</t>
         </is>
       </c>
     </row>
